--- a/data/football/master/football_fixtures.xlsx
+++ b/data/football/master/football_fixtures.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,7 +570,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I1_2026-05-23_Bologna_Inter</t>
+          <t>I1_2026-05-24_Parma_Sassuolo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,73 +594,73 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46165.70833333334</v>
+        <v>46166.58333333334</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="P2" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="X2" t="n">
-        <v>2.36</v>
+        <v>1.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -674,104 +674,104 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B1_2026-05-23_Antwerp_Westerlo</t>
+          <t>SP2_2026-05-24_Albacete_Sociedad B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46165.82291666666</v>
+        <v>46166.63541666666</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Antwerp</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="R3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="X3" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -785,104 +785,104 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B1_2026-05-23_Oud-Heverlee Leuven_Genk</t>
+          <t>SP2_2026-05-24_Andorra_Ceuta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46165.82291666666</v>
+        <v>46166.63541666666</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>5.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>3.73</v>
+        <v>4.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>5.41</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>5.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -896,29 +896,29 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B1_2026-05-23_Standard_Charleroi</t>
+          <t>E0_2026-05-24_Brighton_Man United</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -927,73 +927,73 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46165.82291666666</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Man United</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="P5" t="n">
-        <v>3.35</v>
+        <v>3.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1007,29 +1007,29 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I1_2026-05-23_Lazio_Pisa</t>
+          <t>E0_2026-05-24_Burnley_Wolves</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1038,73 +1038,73 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46165.82291666666</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>2.36</v>
       </c>
       <c r="P6" t="n">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.76</v>
+        <v>2.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>2.48</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1118,29 +1118,29 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Alaves_Vallecano</t>
+          <t>E0_2026-05-24_Crystal Palace_Arsenal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1149,73 +1149,73 @@
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.41</v>
+        <v>4.13</v>
       </c>
       <c r="P7" t="n">
-        <v>3.31</v>
+        <v>3.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.82</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1229,29 +1229,29 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Betis_Levante</t>
+          <t>E0_2026-05-24_Fulham_Newcastle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1260,73 +1260,73 @@
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.25</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O8" t="n">
-        <v>2.19</v>
+        <v>2.82</v>
       </c>
       <c r="P8" t="n">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.26</v>
+        <v>2.27</v>
       </c>
       <c r="R8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.25</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1340,29 +1340,29 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Celta_Sevilla</t>
+          <t>E0_2026-05-24_Liverpool_Brentford</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1371,73 +1371,73 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Celta</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.8</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.75</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.68</v>
+        <v>4.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.52</v>
+        <v>3.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="T9" t="n">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>1.87</v>
+        <v>2.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1451,29 +1451,29 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Espanol_Sociedad</t>
+          <t>E0_2026-05-24_Man City_Aston Villa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1482,74 +1482,74 @@
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Espanol</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sociedad</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
         <v>3.5</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="W10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.55</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>football-data.co.uk fixtures</t>
@@ -1562,29 +1562,29 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Getafe_Osasuna</t>
+          <t>E0_2026-05-24_Nott'm Forest_Bournemouth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1593,73 +1593,73 @@
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Nott'm Forest</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.41</v>
+        <v>3.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.77</v>
+        <v>3.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>3.66</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="W11" t="n">
-        <v>2.68</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1673,29 +1673,29 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Girona_Elche</t>
+          <t>E0_2026-05-24_Sunderland_Chelsea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1704,55 +1704,55 @@
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.76</v>
+        <v>3.47</v>
       </c>
       <c r="P12" t="n">
-        <v>3.86</v>
+        <v>3.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.16</v>
+        <v>1.99</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>3.65</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>4.45</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
         <v>1.73</v>
@@ -1761,16 +1761,16 @@
         <v>2.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1784,29 +1784,29 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Mallorca_Oviedo</t>
+          <t>E0_2026-05-24_Tottenham_Everton</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1815,73 +1815,73 @@
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="P13" t="n">
-        <v>4.33</v>
+        <v>3.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.9</v>
+        <v>3.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1895,29 +1895,29 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Real Madrid_Ath Bilbao</t>
+          <t>E0_2026-05-24_West Ham_Leeds</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>E0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1926,73 +1926,73 @@
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.66666666666</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="P14" t="n">
-        <v>4.63</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.84</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>2.57</v>
+        <v>2.19</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2006,29 +2006,29 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SP1_2026-05-23_Valencia_Barcelona</t>
+          <t>I1_2026-05-24_Napoli_Udinese</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2037,73 +2037,73 @@
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46165.83333333334</v>
+        <v>46166.70833333334</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
       <c r="P15" t="n">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>6.72</v>
       </c>
       <c r="R15" t="n">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="T15" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.91</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2117,29 +2117,29 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I1_2026-05-24_Parma_Sassuolo</t>
+          <t>B1_2026-05-24_Club Brugge_Gent</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2152,69 +2152,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46166.58333333334</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.63</v>
-      </c>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>2.61</v>
+        <v>1.72</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.55</v>
+        <v>3.67</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.95</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>1.87</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>1.87</v>
+        <v>2.86</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2228,34 +2218,34 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SP2_2026-05-24_Albacete_Sociedad B</t>
+          <t>B1_2026-05-24_St Truiden_Mechelen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SP2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>La Liga 2</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tier 2 - Europe Depth</t>
+          <t>Tier 1 - Elite Europe</t>
         </is>
       </c>
       <c r="F17" s="1" t="n">
@@ -2263,69 +2253,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46166.63541666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>St Truiden</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.75</v>
-      </c>
+          <t>Mechelen</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="P17" t="n">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.72</v>
+        <v>3.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.15</v>
-      </c>
+        <v>3.65</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="X17" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2339,34 +2319,34 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SP2_2026-05-24_Andorra_Ceuta</t>
+          <t>B1_2026-05-24_St. Gilloise_Anderlecht</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SP2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>La Liga 2</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tier 2 - Europe Depth</t>
+          <t>Tier 1 - Elite Europe</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
@@ -2374,69 +2354,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46166.63541666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>St. Gilloise</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.25</v>
-      </c>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>4.39</v>
+        <v>4.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.41</v>
+        <v>6.26</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="T18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2.5</v>
-      </c>
+        <v>6.66</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="X18" t="n">
-        <v>2.47</v>
+        <v>2.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2450,34 +2420,34 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Brighton_Man United</t>
+          <t>SP2_2026-05-24_Cadiz_Leganes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
@@ -2485,69 +2455,69 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Man United</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.85</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2561,34 +2531,34 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Burnley_Wolves</t>
+          <t>SP2_2026-05-24_Cultural Leonesa_Burgos</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
@@ -2596,69 +2566,69 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cultural Leonesa</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.35</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="V20" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>2.31</v>
       </c>
       <c r="X20" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2672,34 +2642,34 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Crystal Palace_Arsenal</t>
+          <t>SP2_2026-05-24_Eibar_Cordoba</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
@@ -2707,69 +2677,69 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M21" t="n">
         <v>4.2</v>
       </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4.13</v>
+        <v>1.68</v>
       </c>
       <c r="P21" t="n">
-        <v>3.86</v>
+        <v>3.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.76</v>
+        <v>4.29</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>1.71</v>
       </c>
       <c r="S21" t="n">
         <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.82</v>
+        <v>4.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V21" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="X21" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2783,34 +2753,34 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Fulham_Newcastle</t>
+          <t>SP2_2026-05-24_Huesca_Castellon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
@@ -2818,69 +2788,69 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
         <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
-        <v>2.82</v>
+        <v>4.34</v>
       </c>
       <c r="P22" t="n">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X22" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2894,34 +2864,34 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Liverpool_Brentford</t>
+          <t>SP2_2026-05-24_Las Palmas_Zaragoza</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
@@ -2929,69 +2899,69 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.8</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="V23" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.8</v>
       </c>
-      <c r="P23" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z23" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3005,34 +2975,34 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Man City_Aston Villa</t>
+          <t>SP2_2026-05-24_Malaga_Santander</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
@@ -3040,69 +3010,69 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="P24" t="n">
-        <v>5.93</v>
+        <v>4.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.390000000000001</v>
+        <v>4.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="S24" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>9.5</v>
+        <v>4.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3116,34 +3086,34 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Nott'm Forest_Bournemouth</t>
+          <t>SP2_2026-05-24_Mirandes_Granada</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
@@ -3151,69 +3121,69 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nott'm Forest</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>5.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.19</v>
+        <v>1.57</v>
       </c>
       <c r="P25" t="n">
-        <v>3.72</v>
+        <v>3.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>4.91</v>
       </c>
       <c r="R25" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="V25" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="X25" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3227,34 +3197,34 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Sunderland_Chelsea</t>
+          <t>SP2_2026-05-24_Sp Gijon_Almeria</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
@@ -3262,69 +3232,69 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sp Gijon</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="O26" t="n">
-        <v>3.47</v>
+        <v>4.01</v>
       </c>
       <c r="P26" t="n">
-        <v>3.59</v>
+        <v>3.89</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="R26" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="X26" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3338,34 +3308,34 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_Tottenham_Everton</t>
+          <t>SP2_2026-05-24_Valladolid_La Coruna</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>SP2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>La Liga 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tier 1 - Elite Europe</t>
+          <t>Tier 2 - Europe Depth</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
@@ -3373,69 +3343,69 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.72916666666</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>La Coruna</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>1.89</v>
+        <v>5.03</v>
       </c>
       <c r="P27" t="n">
-        <v>3.63</v>
+        <v>3.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.78</v>
+        <v>1.57</v>
       </c>
       <c r="R27" t="n">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="S27" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>4.3</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="V27" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="W27" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="X27" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3449,29 +3419,29 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E0_2026-05-24_West Ham_Leeds</t>
+          <t>I1_2026-05-24_Cremonese_Como</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3484,51 +3454,51 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.82291666666</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>5.25</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>1.82</v>
+        <v>5.33</v>
       </c>
       <c r="P28" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.88</v>
+        <v>5.66</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="U28" t="n">
         <v>1.67</v>
@@ -3537,16 +3507,16 @@
         <v>2.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X28" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3560,14 +3530,14 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>I1_2026-05-24_Napoli_Udinese</t>
+          <t>I1_2026-05-24_Lecce_Genoa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3595,69 +3565,69 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.82291666666</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="P29" t="n">
-        <v>4.07</v>
+        <v>3.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.72</v>
+        <v>4.84</v>
       </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="S29" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="W29" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="X29" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3671,29 +3641,29 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B1_2026-05-24_Club Brugge_Gent</t>
+          <t>I1_2026-05-24_Milan_Cagliari</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3706,59 +3676,69 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.82291666666</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11</v>
+      </c>
       <c r="O30" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.67</v>
+        <v>10.35</v>
       </c>
       <c r="R30" t="n">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="T30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.2</v>
+      </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="X30" t="n">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -3772,29 +3752,29 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B1_2026-05-24_St Truiden_Mechelen</t>
+          <t>I1_2026-05-24_Torino_Juventus</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3807,59 +3787,69 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.82291666666</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>St Truiden</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Mechelen</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.42</v>
+      </c>
       <c r="O31" t="n">
-        <v>1.82</v>
+        <v>7.23</v>
       </c>
       <c r="P31" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.53</v>
+        <v>1.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.88</v>
+        <v>7.5</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="T31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+        <v>1.44</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.1</v>
+      </c>
       <c r="W31" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="X31" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -3873,29 +3863,29 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B1_2026-05-24_St. Gilloise_Anderlecht</t>
+          <t>I1_2026-05-24_Verona_Roma</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3908,59 +3898,69 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.82291666666</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>St. Gilloise</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>9.84</v>
       </c>
       <c r="P32" t="n">
-        <v>4.2</v>
+        <v>5.01</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.26</v>
+        <v>1.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="S32" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="T32" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+        <v>1.35</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2</v>
+      </c>
       <c r="W32" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="X32" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -3974,24 +3974,24 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SP2_2026-05-24_Cadiz_Leganes</t>
+          <t>SP1_2026-05-24_Villarreal_Ath Madrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SP2</t>
+          <t>SP1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La Liga 2</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tier 2 - Europe Depth</t>
+          <t>Tier 1 - Elite Europe</t>
         </is>
       </c>
       <c r="F33" s="1" t="n">
@@ -4009,69 +4009,69 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.83333333334</v>
       </c>
       <c r="I33" t="b">
         <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Ath Madrid</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="P33" t="n">
-        <v>3.24</v>
+        <v>3.71</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="W33" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="X33" t="n">
-        <v>1.85</v>
+        <v>2.63</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4085,1561 +4085,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Cultural Leonesa_Burgos</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Cultural Leonesa</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Eibar_Cordoba</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Eibar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Cordoba</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P35" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Huesca_Castellon</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Huesca</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Castellon</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R36" t="n">
-        <v>5</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Las Palmas_Zaragoza</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Zaragoza</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N37" t="n">
-        <v>7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>2</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Malaga_Santander</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Mirandes_Granada</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H39" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Mirandes</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Sp Gijon_Almeria</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Sp Gijon</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Almeria</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="M40" t="n">
-        <v>4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O40" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="P40" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-24_Valladolid_La Coruna</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>46166.72916666666</v>
-      </c>
-      <c r="I41" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>La Coruna</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O41" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="P41" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>I1_2026-05-24_Cremonese_Como</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>46166.82291666666</v>
-      </c>
-      <c r="I42" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O42" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="P42" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R42" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>I1_2026-05-24_Lecce_Genoa</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>46166.82291666666</v>
-      </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T43" t="n">
-        <v>5</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>I1_2026-05-24_Milan_Cagliari</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>46166.82291666666</v>
-      </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>11</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P44" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>11</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>I1_2026-05-24_Torino_Juventus</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>46166.82291666666</v>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O45" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="P45" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>I1_2026-05-24_Verona_Roma</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>46166.82291666666</v>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Roma</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O46" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="P46" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R46" t="n">
-        <v>13</v>
-      </c>
-      <c r="S46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SP1_2026-05-24_Villarreal_Ath Madrid</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SP1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>46166.83333333334</v>
-      </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Ath Madrid</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2026-05-23 08:51:30</t>
+          <t>2026-05-24 05:45:49</t>
         </is>
       </c>
     </row>
